--- a/ru/downloads/data-excel/1.2.1.1.xlsx
+++ b/ru/downloads/data-excel/1.2.1.1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882E850F-AA01-4024-B749-7C1E7E334C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист" sheetId="1" r:id="rId1"/>
@@ -28,12 +29,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -227,18 +222,9 @@
     <t>Kyrgyz Republic</t>
   </si>
   <si>
-    <t>1.2.1.1a Уровень бедности среди занятого населения согласно официальной черте бедности</t>
-  </si>
-  <si>
-    <t>1.2.1.1a Proportion of employed population living below the official poverty line</t>
-  </si>
-  <si>
     <t>…</t>
   </si>
   <si>
-    <t>1.2.1.1а Расмий кедейчиликтин чегине ылайык иш менен камсыз болгон калктын арасындагы жакырчылыктын деңгээли</t>
-  </si>
-  <si>
     <t>Айыл чарба, токой чарбасы жана балык уулоо</t>
   </si>
   <si>
@@ -375,17 +361,26 @@
   </si>
   <si>
     <t>Village</t>
+  </si>
+  <si>
+    <t>1.2.1.1 Proportion of employed population living below the official poverty line</t>
+  </si>
+  <si>
+    <t>1.2.1.1 Уровень бедности среди занятого населения согласно официальной черте бедности</t>
+  </si>
+  <si>
+    <t>1.2.1.1 Расмий кедейчиликтин чегине ылайык иш менен камсыз болгон калктын арасындагы жакырчылыктын деңгээли</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -502,6 +497,12 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -566,11 +567,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -584,61 +585,47 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -646,49 +633,39 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Normal 17" xfId="4"/>
+    <cellStyle name="Normal 17" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
-    <cellStyle name="Обычный 6" xfId="2"/>
-    <cellStyle name="Обычный 7" xfId="5"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный 6" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный 7" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
     <cellStyle name="Финансовый" xfId="3" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -705,7 +682,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Data"/>
@@ -8431,8 +8408,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L47"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.5703125" customWidth="1"/>
@@ -8441,22 +8418,22 @@
     <col min="4" max="7" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
+        <v>109</v>
+      </c>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -8466,21 +8443,21 @@
       <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="20"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
     </row>
-    <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="20"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
+    <row r="3" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
     </row>
-    <row r="4" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -8493,1559 +8470,1680 @@
       <c r="D4" s="7">
         <v>2015</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <v>2016</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="7">
         <v>2017</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="7">
         <v>2018</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="7">
         <v>2019</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="7">
         <v>2020</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4" s="7">
         <v>2021</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4" s="7">
         <v>2022</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="7">
         <v>2023</v>
       </c>
+      <c r="M4" s="7">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:13" s="29" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="27">
+        <v>22.971916353735754</v>
+      </c>
+      <c r="E5" s="27">
+        <v>18.3</v>
+      </c>
+      <c r="F5" s="27">
+        <v>18</v>
+      </c>
+      <c r="G5" s="27">
+        <v>15.5</v>
+      </c>
+      <c r="H5" s="28">
+        <v>13.2</v>
+      </c>
+      <c r="I5" s="28">
+        <v>17.2</v>
+      </c>
+      <c r="J5" s="31">
+        <v>24.7</v>
+      </c>
+      <c r="K5" s="28">
+        <v>24.2</v>
+      </c>
+      <c r="L5" s="28">
+        <v>21.9</v>
+      </c>
+      <c r="M5" s="28">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="28"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="37">
-        <v>22.971916353735754</v>
-      </c>
-      <c r="E5" s="37">
+      <c r="D7" s="12">
+        <v>24.625380526353009</v>
+      </c>
+      <c r="E7" s="12">
+        <v>19.7</v>
+      </c>
+      <c r="F7" s="12">
+        <v>20</v>
+      </c>
+      <c r="G7" s="12">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="H7" s="12">
+        <v>14.9</v>
+      </c>
+      <c r="I7" s="12">
+        <v>18.7</v>
+      </c>
+      <c r="J7" s="12">
+        <v>26.3</v>
+      </c>
+      <c r="K7" s="12">
+        <v>25.5</v>
+      </c>
+      <c r="L7" s="12">
+        <v>23.2</v>
+      </c>
+      <c r="M7" s="34">
+        <v>18.399999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="13">
+        <v>20.568799401966807</v>
+      </c>
+      <c r="E8" s="13">
+        <v>16</v>
+      </c>
+      <c r="F8" s="13">
+        <v>14.8</v>
+      </c>
+      <c r="G8" s="13">
+        <v>13.6</v>
+      </c>
+      <c r="H8" s="26">
+        <v>10.5</v>
+      </c>
+      <c r="I8" s="26">
+        <v>14.9</v>
+      </c>
+      <c r="J8" s="13">
+        <v>22</v>
+      </c>
+      <c r="K8" s="26">
+        <v>22.3</v>
+      </c>
+      <c r="L8" s="26">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="M8" s="34">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="34"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="14">
+        <v>23.727491891830027</v>
+      </c>
+      <c r="E10" s="14">
+        <v>18.981761935247256</v>
+      </c>
+      <c r="F10" s="14">
+        <v>14.748616757210716</v>
+      </c>
+      <c r="G10" s="14">
+        <v>12.56931186247461</v>
+      </c>
+      <c r="H10" s="14">
+        <v>6.6</v>
+      </c>
+      <c r="I10" s="14">
+        <v>11.4</v>
+      </c>
+      <c r="J10" s="14">
+        <v>18</v>
+      </c>
+      <c r="K10" s="14">
+        <v>18</v>
+      </c>
+      <c r="L10" s="14">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="M10" s="34">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="14">
+        <v>19.900404104368668</v>
+      </c>
+      <c r="E11" s="14">
+        <v>18.030501185267081</v>
+      </c>
+      <c r="F11" s="14">
+        <v>13.948052664523717</v>
+      </c>
+      <c r="G11" s="14">
+        <v>10.713886021727234</v>
+      </c>
+      <c r="H11" s="14">
+        <v>8.1</v>
+      </c>
+      <c r="I11" s="14">
+        <v>8.9</v>
+      </c>
+      <c r="J11" s="14">
+        <v>17.2</v>
+      </c>
+      <c r="K11" s="14">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="L11" s="14">
+        <v>14.7</v>
+      </c>
+      <c r="M11" s="34">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="14">
+        <v>20.936837214778837</v>
+      </c>
+      <c r="E12" s="14">
+        <v>17.480641986834843</v>
+      </c>
+      <c r="F12" s="14">
+        <v>18.451453227304977</v>
+      </c>
+      <c r="G12" s="14">
+        <v>15.811220408739953</v>
+      </c>
+      <c r="H12" s="14">
+        <v>11.1</v>
+      </c>
+      <c r="I12" s="14">
+        <v>15.3</v>
+      </c>
+      <c r="J12" s="14">
+        <v>23.2</v>
+      </c>
+      <c r="K12" s="14">
+        <v>21.3</v>
+      </c>
+      <c r="L12" s="14">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="M12" s="34">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="14">
+        <v>31.941973691113994</v>
+      </c>
+      <c r="E13" s="14">
+        <v>22.514499275320098</v>
+      </c>
+      <c r="F13" s="14">
+        <v>22.859645557225814</v>
+      </c>
+      <c r="G13" s="14">
+        <v>18.364476580609249</v>
+      </c>
+      <c r="H13" s="14">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="I13" s="14">
+        <v>22.1</v>
+      </c>
+      <c r="J13" s="14">
+        <v>29.1</v>
+      </c>
+      <c r="K13" s="14">
+        <v>30.2</v>
+      </c>
+      <c r="L13" s="14">
+        <v>29.1</v>
+      </c>
+      <c r="M13" s="34">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="14">
+        <v>33.358438093348205</v>
+      </c>
+      <c r="E14" s="14">
+        <v>27.556783086958745</v>
+      </c>
+      <c r="F14" s="14">
+        <v>26.449236982189937</v>
+      </c>
+      <c r="G14" s="14">
+        <v>23.421118218014087</v>
+      </c>
+      <c r="H14" s="14">
+        <v>25</v>
+      </c>
+      <c r="I14" s="14">
+        <v>27.5</v>
+      </c>
+      <c r="J14" s="14">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="K14" s="14">
+        <v>31.7</v>
+      </c>
+      <c r="L14" s="14">
+        <v>28.3</v>
+      </c>
+      <c r="M14" s="34">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="14">
+        <v>27.540969086733867</v>
+      </c>
+      <c r="E15" s="14">
+        <v>20.070138927127417</v>
+      </c>
+      <c r="F15" s="14">
+        <v>21.848722918967393</v>
+      </c>
+      <c r="G15" s="14">
+        <v>18.51925367661957</v>
+      </c>
+      <c r="H15" s="14">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="I15" s="14">
+        <v>25.2</v>
+      </c>
+      <c r="J15" s="14">
+        <v>33.4</v>
+      </c>
+      <c r="K15" s="14">
+        <v>34.1</v>
+      </c>
+      <c r="L15" s="14">
+        <v>33.4</v>
+      </c>
+      <c r="M15" s="34">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="14">
+        <v>20.291456975420921</v>
+      </c>
+      <c r="E16" s="14">
+        <v>15.102516529601948</v>
+      </c>
+      <c r="F16" s="14">
+        <v>15.280590240825578</v>
+      </c>
+      <c r="G16" s="14">
+        <v>13.517279633635679</v>
+      </c>
+      <c r="H16" s="14">
+        <v>11.1</v>
+      </c>
+      <c r="I16" s="14">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="J16" s="14">
+        <v>26.4</v>
+      </c>
+      <c r="K16" s="14">
+        <v>25.8</v>
+      </c>
+      <c r="L16" s="14">
+        <v>22.1</v>
+      </c>
+      <c r="M16" s="34">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="14">
+        <v>12.363589530005411</v>
+      </c>
+      <c r="E17" s="14">
+        <v>11.302523667429019</v>
+      </c>
+      <c r="F17" s="14">
+        <v>10.786084047642252</v>
+      </c>
+      <c r="G17" s="14">
+        <v>12.477862268683602</v>
+      </c>
+      <c r="H17" s="14">
+        <v>8.6</v>
+      </c>
+      <c r="I17" s="14">
+        <v>12.3</v>
+      </c>
+      <c r="J17" s="14">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="K17" s="14">
+        <v>20</v>
+      </c>
+      <c r="L17" s="14">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="M17" s="34">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="14">
+        <v>11.3934157044781</v>
+      </c>
+      <c r="E18" s="14">
+        <v>8.3983705266624522</v>
+      </c>
+      <c r="F18" s="14">
+        <v>10.34486128229991</v>
+      </c>
+      <c r="G18" s="14">
+        <v>9.4892565740388939</v>
+      </c>
+      <c r="H18" s="14">
+        <v>7.9</v>
+      </c>
+      <c r="I18" s="14">
+        <v>8.9</v>
+      </c>
+      <c r="J18" s="14">
+        <v>13</v>
+      </c>
+      <c r="K18" s="14">
+        <v>12.1</v>
+      </c>
+      <c r="L18" s="14">
+        <v>14.7</v>
+      </c>
+      <c r="M18" s="34">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="14">
+        <v>9.4370766036096025</v>
+      </c>
+      <c r="E19" s="14">
+        <v>14.236349327004385</v>
+      </c>
+      <c r="F19" s="14">
+        <v>14.339166341825397</v>
+      </c>
+      <c r="G19" s="14">
+        <v>11.956666877329058</v>
+      </c>
+      <c r="H19" s="14">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="I19" s="14">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="J19" s="14">
+        <v>14.3</v>
+      </c>
+      <c r="K19" s="14">
+        <v>10.3</v>
+      </c>
+      <c r="L19" s="14">
+        <v>9.1</v>
+      </c>
+      <c r="M19" s="34">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="14">
+        <v>5.3483560499368208</v>
+      </c>
+      <c r="E20" s="14">
+        <v>7.6176247728212596</v>
+      </c>
+      <c r="F20" s="14">
+        <v>6.1521676850850815</v>
+      </c>
+      <c r="G20" s="14">
+        <v>4.7759391183563746</v>
+      </c>
+      <c r="H20" s="14">
+        <v>4.2</v>
+      </c>
+      <c r="I20" s="14">
+        <v>9.4</v>
+      </c>
+      <c r="J20" s="14">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="K20" s="14">
+        <v>15.1</v>
+      </c>
+      <c r="L20" s="14">
+        <v>12.5</v>
+      </c>
+      <c r="M20" s="34">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="14">
+        <v>4.3248118918794747</v>
+      </c>
+      <c r="E21" s="14">
+        <v>13.92994136929909</v>
+      </c>
+      <c r="F21" s="14">
+        <v>10.576621203348067</v>
+      </c>
+      <c r="G21" s="14">
+        <v>3.7174719620012309</v>
+      </c>
+      <c r="H21" s="14">
+        <v>7.3</v>
+      </c>
+      <c r="I21" s="14">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="J21" s="14">
+        <v>13.6</v>
+      </c>
+      <c r="K21" s="14">
+        <v>12.1</v>
+      </c>
+      <c r="L21" s="14">
+        <v>11.6</v>
+      </c>
+      <c r="M21" s="34">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="34"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" s="12">
+        <v>18.096777347528821</v>
+      </c>
+      <c r="E23" s="12">
+        <v>11.846666849488686</v>
+      </c>
+      <c r="F23" s="12">
+        <v>13.174611461584712</v>
+      </c>
+      <c r="G23" s="12">
+        <v>13</v>
+      </c>
+      <c r="H23" s="14">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="I23" s="14">
+        <v>12.4</v>
+      </c>
+      <c r="J23" s="12">
+        <v>24.8</v>
+      </c>
+      <c r="K23" s="14">
+        <v>25.9</v>
+      </c>
+      <c r="L23" s="14">
+        <v>22.6</v>
+      </c>
+      <c r="M23" s="34">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24" s="13">
+        <v>25.484816175693549</v>
+      </c>
+      <c r="E24" s="13">
+        <v>21.760369334408139</v>
+      </c>
+      <c r="F24" s="13">
+        <v>20.74075673507425</v>
+      </c>
+      <c r="G24" s="13">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="H24" s="14">
+        <v>15.2</v>
+      </c>
+      <c r="I24" s="14">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="J24" s="13">
+        <v>24.6</v>
+      </c>
+      <c r="K24" s="14">
+        <v>23.2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>21.5</v>
+      </c>
+      <c r="M24" s="34">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="34"/>
+    </row>
+    <row r="26" spans="1:13" ht="24" x14ac:dyDescent="0.25">
+      <c r="A26" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="14">
+        <v>29.143908007004935</v>
+      </c>
+      <c r="E26" s="14">
+        <v>24.458296607773754</v>
+      </c>
+      <c r="F26" s="14">
+        <v>22.569517630180179</v>
+      </c>
+      <c r="G26" s="14">
+        <v>21.917680212784951</v>
+      </c>
+      <c r="H26" s="14">
+        <v>14.2</v>
+      </c>
+      <c r="I26" s="14">
+        <v>21.1</v>
+      </c>
+      <c r="J26" s="14">
+        <v>24.3</v>
+      </c>
+      <c r="K26" s="14">
+        <v>25.9</v>
+      </c>
+      <c r="L26" s="14">
+        <v>24.3</v>
+      </c>
+      <c r="M26" s="34">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="14">
+        <v>25.706732621123876</v>
+      </c>
+      <c r="E27" s="14">
+        <v>17.407081439088394</v>
+      </c>
+      <c r="F27" s="14">
+        <v>43.485033074010154</v>
+      </c>
+      <c r="G27" s="14">
+        <v>46.524661279291919</v>
+      </c>
+      <c r="H27" s="14">
+        <v>40.4</v>
+      </c>
+      <c r="I27" s="14">
+        <v>40.1</v>
+      </c>
+      <c r="J27" s="14">
+        <v>47.1</v>
+      </c>
+      <c r="K27" s="14">
+        <v>48.3</v>
+      </c>
+      <c r="L27" s="14">
+        <v>44.96</v>
+      </c>
+      <c r="M27" s="34">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" s="14">
+        <v>20.686606210854819</v>
+      </c>
+      <c r="E28" s="14">
+        <v>16.804166833395346</v>
+      </c>
+      <c r="F28" s="14">
+        <v>19.252254610641589</v>
+      </c>
+      <c r="G28" s="14">
+        <v>12.973926140370661</v>
+      </c>
+      <c r="H28" s="14">
+        <v>14.3</v>
+      </c>
+      <c r="I28" s="14">
+        <v>13.5</v>
+      </c>
+      <c r="J28" s="14">
+        <v>23.6</v>
+      </c>
+      <c r="K28" s="14">
+        <v>24.3</v>
+      </c>
+      <c r="L28" s="14">
+        <v>22.5</v>
+      </c>
+      <c r="M28" s="34">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="24" x14ac:dyDescent="0.25">
+      <c r="A29" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="14">
+        <v>10.380818288468426</v>
+      </c>
+      <c r="E29" s="14">
+        <v>6.694579441234457</v>
+      </c>
+      <c r="F29" s="14">
+        <v>16.766197552453242</v>
+      </c>
+      <c r="G29" s="14">
+        <v>9.8700006382711329</v>
+      </c>
+      <c r="H29" s="14">
+        <v>10</v>
+      </c>
+      <c r="I29" s="14">
+        <v>18.7</v>
+      </c>
+      <c r="J29" s="14">
+        <v>28.8</v>
+      </c>
+      <c r="K29" s="14">
+        <v>28.1</v>
+      </c>
+      <c r="L29" s="14">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="M29" s="34">
+        <v>18.600000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="36" x14ac:dyDescent="0.25">
+      <c r="A30" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" s="14">
+        <v>8.7634580318953859</v>
+      </c>
+      <c r="E30" s="14">
+        <v>11.046114565895568</v>
+      </c>
+      <c r="F30" s="14">
+        <v>16.935337550642007</v>
+      </c>
+      <c r="G30" s="14">
+        <v>14.440148321432762</v>
+      </c>
+      <c r="H30" s="14">
+        <v>16.3</v>
+      </c>
+      <c r="I30" s="14">
+        <v>24.4</v>
+      </c>
+      <c r="J30" s="14">
+        <v>27.8</v>
+      </c>
+      <c r="K30" s="14">
+        <v>25.8</v>
+      </c>
+      <c r="L30" s="14">
+        <v>30</v>
+      </c>
+      <c r="M30" s="34">
+        <v>18.899999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="14">
+        <v>30.479758516587125</v>
+      </c>
+      <c r="E31" s="14">
+        <v>21.910700739938726</v>
+      </c>
+      <c r="F31" s="14">
+        <v>25.189652676651377</v>
+      </c>
+      <c r="G31" s="14">
+        <v>18.342747525957986</v>
+      </c>
+      <c r="H31" s="14">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="I31" s="14">
+        <v>21.6</v>
+      </c>
+      <c r="J31" s="14">
+        <v>29.9</v>
+      </c>
+      <c r="K31" s="14">
+        <v>27.1</v>
+      </c>
+      <c r="L31" s="14">
+        <v>25.3</v>
+      </c>
+      <c r="M31" s="34">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="24" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" s="14">
+        <v>17.048203277049947</v>
+      </c>
+      <c r="E32" s="14">
+        <v>13.904378994106649</v>
+      </c>
+      <c r="F32" s="14">
+        <v>12.6648830342567</v>
+      </c>
+      <c r="G32" s="14">
+        <v>12.403590756556879</v>
+      </c>
+      <c r="H32" s="14">
+        <v>11.6</v>
+      </c>
+      <c r="I32" s="14">
+        <v>10.1</v>
+      </c>
+      <c r="J32" s="14">
+        <v>20.7</v>
+      </c>
+      <c r="K32" s="14">
+        <v>20.7</v>
+      </c>
+      <c r="L32" s="14">
+        <v>21</v>
+      </c>
+      <c r="M32" s="34">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" s="14">
+        <v>22.274049816094269</v>
+      </c>
+      <c r="E33" s="14">
+        <v>20.940255499025756</v>
+      </c>
+      <c r="F33" s="14">
+        <v>17.991689994650695</v>
+      </c>
+      <c r="G33" s="14">
+        <v>14.19051856054139</v>
+      </c>
+      <c r="H33" s="14">
+        <v>15.2</v>
+      </c>
+      <c r="I33" s="14">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="J33" s="14">
+        <v>26.2</v>
+      </c>
+      <c r="K33" s="14">
+        <v>24.3</v>
+      </c>
+      <c r="L33" s="14">
+        <v>22</v>
+      </c>
+      <c r="M33" s="34">
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="24" x14ac:dyDescent="0.25">
+      <c r="A34" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D34" s="14">
+        <v>18.210339702711089</v>
+      </c>
+      <c r="E34" s="14">
+        <v>13.950839004406477</v>
+      </c>
+      <c r="F34" s="14">
+        <v>10.454912304521647</v>
+      </c>
+      <c r="G34" s="14">
+        <v>10.100326551559347</v>
+      </c>
+      <c r="H34" s="14">
+        <v>8.9</v>
+      </c>
+      <c r="I34" s="14">
+        <v>11.6</v>
+      </c>
+      <c r="J34" s="14">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="K34" s="14">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="L34" s="14">
+        <v>15</v>
+      </c>
+      <c r="M34" s="34">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="14">
+        <v>23.378289047105444</v>
+      </c>
+      <c r="E35" s="14">
+        <v>12.552140899407622</v>
+      </c>
+      <c r="F35" s="14">
+        <v>7.2176300468835244</v>
+      </c>
+      <c r="G35" s="14">
+        <v>7.398290201001557</v>
+      </c>
+      <c r="H35" s="14">
+        <v>2.1</v>
+      </c>
+      <c r="I35" s="14">
+        <v>5.3</v>
+      </c>
+      <c r="J35" s="14">
+        <v>10.7</v>
+      </c>
+      <c r="K35" s="14">
+        <v>7.5</v>
+      </c>
+      <c r="L35" s="14">
+        <v>6.3</v>
+      </c>
+      <c r="M35" s="34">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D36" s="14">
+        <v>10.489031113365179</v>
+      </c>
+      <c r="E36" s="14">
+        <v>6.9730957623240366</v>
+      </c>
+      <c r="F36" s="14">
+        <v>11.910368149341213</v>
+      </c>
+      <c r="G36" s="14">
+        <v>10.729114750103726</v>
+      </c>
+      <c r="H36" s="14">
+        <v>15.6</v>
+      </c>
+      <c r="I36" s="14">
+        <v>20.5</v>
+      </c>
+      <c r="J36" s="14">
+        <v>28.9</v>
+      </c>
+      <c r="K36" s="14">
+        <v>11.4</v>
+      </c>
+      <c r="L36" s="14">
+        <v>9</v>
+      </c>
+      <c r="M36" s="34">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D37" s="14">
+        <v>3.9345552103031651</v>
+      </c>
+      <c r="E37" s="14">
+        <v>1.5610395489662543</v>
+      </c>
+      <c r="F37" s="14">
+        <v>1.8769969620631242</v>
+      </c>
+      <c r="G37" s="12"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="30">
+        <v>9</v>
+      </c>
+      <c r="J37" s="14">
+        <v>22.7</v>
+      </c>
+      <c r="K37" s="30">
+        <v>36.5</v>
+      </c>
+      <c r="L37" s="30">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="M37" s="34">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="24" x14ac:dyDescent="0.25">
+      <c r="A38" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="14">
+        <v>18.961062865334473</v>
+      </c>
+      <c r="E38" s="14">
+        <v>6.4150369668849034</v>
+      </c>
+      <c r="F38" s="14">
+        <v>10.73328466572039</v>
+      </c>
+      <c r="G38" s="14">
+        <v>6.1871817427579057</v>
+      </c>
+      <c r="H38" s="14">
+        <v>12.6</v>
+      </c>
+      <c r="I38" s="14">
+        <v>21</v>
+      </c>
+      <c r="J38" s="14">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="K38" s="14">
+        <v>17.8</v>
+      </c>
+      <c r="L38" s="14">
+        <v>12</v>
+      </c>
+      <c r="M38" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="24" x14ac:dyDescent="0.25">
+      <c r="A39" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D39" s="14">
+        <v>13.647895195863507</v>
+      </c>
+      <c r="E39" s="14">
+        <v>9.7394396593161634</v>
+      </c>
+      <c r="F39" s="14">
+        <v>17.445705080152951</v>
+      </c>
+      <c r="G39" s="14">
+        <v>10.903917301963624</v>
+      </c>
+      <c r="H39" s="14">
+        <v>10.8</v>
+      </c>
+      <c r="I39" s="14">
+        <v>12</v>
+      </c>
+      <c r="J39" s="14">
+        <v>24.9</v>
+      </c>
+      <c r="K39" s="14">
+        <v>20.3</v>
+      </c>
+      <c r="L39" s="14">
+        <v>41.3</v>
+      </c>
+      <c r="M39" s="34">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="24" x14ac:dyDescent="0.25">
+      <c r="A40" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D40" s="14">
+        <v>16.876778837009706</v>
+      </c>
+      <c r="E40" s="14">
+        <v>9.9482201054391233</v>
+      </c>
+      <c r="F40" s="14">
+        <v>10.126908927702534</v>
+      </c>
+      <c r="G40" s="14">
+        <v>6.6467604972894136</v>
+      </c>
+      <c r="H40" s="14">
+        <v>6.7</v>
+      </c>
+      <c r="I40" s="14">
+        <v>13.1</v>
+      </c>
+      <c r="J40" s="14">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="K40" s="14">
+        <v>20.5</v>
+      </c>
+      <c r="L40" s="14">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="M40" s="34">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" s="14">
+        <v>20.413163685010215</v>
+      </c>
+      <c r="E41" s="14">
+        <v>16.145522408727153</v>
+      </c>
+      <c r="F41" s="14">
+        <v>18.579279969160616</v>
+      </c>
+      <c r="G41" s="14">
+        <v>18.915134715736656</v>
+      </c>
+      <c r="H41" s="14">
+        <v>13.2</v>
+      </c>
+      <c r="I41" s="14">
+        <v>22</v>
+      </c>
+      <c r="J41" s="14">
+        <v>30.7</v>
+      </c>
+      <c r="K41" s="14">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="L41" s="14">
+        <v>25.6</v>
+      </c>
+      <c r="M41" s="34">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="24" x14ac:dyDescent="0.25">
+      <c r="A42" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42" s="14">
+        <v>13.310295070774758</v>
+      </c>
+      <c r="E42" s="14">
+        <v>11.612557015790795</v>
+      </c>
+      <c r="F42" s="14">
+        <v>15.172329167457105</v>
+      </c>
+      <c r="G42" s="14">
+        <v>12.02603404393124</v>
+      </c>
+      <c r="H42" s="14">
+        <v>10.9</v>
+      </c>
+      <c r="I42" s="14">
+        <v>22.9</v>
+      </c>
+      <c r="J42" s="14">
+        <v>25.1</v>
+      </c>
+      <c r="K42" s="14">
+        <v>23.2</v>
+      </c>
+      <c r="L42" s="14">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="M42" s="34">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D43" s="14">
+        <v>24.880927816476003</v>
+      </c>
+      <c r="E43" s="14">
+        <v>22.865183692499258</v>
+      </c>
+      <c r="F43" s="14">
+        <v>13.457394959480895</v>
+      </c>
+      <c r="G43" s="14">
+        <v>9.9681806468962222</v>
+      </c>
+      <c r="H43" s="14">
+        <v>13.3</v>
+      </c>
+      <c r="I43" s="14">
+        <v>12.6</v>
+      </c>
+      <c r="J43" s="14">
+        <v>16.3</v>
+      </c>
+      <c r="K43" s="14">
+        <v>23.8</v>
+      </c>
+      <c r="L43" s="14">
+        <v>15.3</v>
+      </c>
+      <c r="M43" s="34">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D44" s="14">
+        <v>14.316550849178517</v>
+      </c>
+      <c r="E44" s="14">
+        <v>10.525974149433518</v>
+      </c>
+      <c r="F44" s="14">
+        <v>9.6502437264322651</v>
+      </c>
+      <c r="G44" s="14">
+        <v>9.1216159509677954</v>
+      </c>
+      <c r="H44" s="14">
+        <v>6.8</v>
+      </c>
+      <c r="I44" s="14">
+        <v>12.5</v>
+      </c>
+      <c r="J44" s="14">
+        <v>24.3</v>
+      </c>
+      <c r="K44" s="14">
+        <v>21</v>
+      </c>
+      <c r="L44" s="14">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="M44" s="34">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D45" s="14">
+        <v>23.958709378309926</v>
+      </c>
+      <c r="E45" s="14">
+        <v>46.915523465793008</v>
+      </c>
+      <c r="F45" s="14">
+        <v>31.481607442776532</v>
+      </c>
+      <c r="G45" s="14">
+        <v>23.380874333038371</v>
+      </c>
+      <c r="H45" s="14">
         <v>18.3</v>
       </c>
-      <c r="F5" s="37">
+      <c r="I45" s="14">
+        <v>36</v>
+      </c>
+      <c r="J45" s="14">
+        <v>20.6</v>
+      </c>
+      <c r="K45" s="14">
         <v>18</v>
       </c>
-      <c r="G5" s="37">
-        <v>15.5</v>
-      </c>
-      <c r="H5" s="38">
-        <v>13.2</v>
-      </c>
-      <c r="I5" s="38">
-        <v>17.2</v>
-      </c>
-      <c r="J5" s="41">
-        <v>24.7</v>
-      </c>
-      <c r="K5" s="38">
-        <v>24.2</v>
-      </c>
-      <c r="L5" s="38">
-        <v>21.9</v>
+      <c r="L45" s="14">
+        <v>53</v>
+      </c>
+      <c r="M45" s="34">
+        <v>29.1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
+    <row r="46" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D46" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="F46" s="22">
+        <v>15.59978614323523</v>
+      </c>
+      <c r="G46" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="H46" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="I46" s="22">
+        <v>10.7</v>
+      </c>
+      <c r="J46" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="K46" s="22">
+        <v>3.2</v>
+      </c>
+      <c r="L46" s="22">
+        <v>5.2</v>
+      </c>
+      <c r="M46" s="22">
+        <v>29.7</v>
+      </c>
     </row>
-    <row r="7" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" s="14">
-        <v>24.625380526353009</v>
-      </c>
-      <c r="E7" s="14">
-        <v>19.7</v>
-      </c>
-      <c r="F7" s="14">
-        <v>20</v>
-      </c>
-      <c r="G7" s="14">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="H7" s="14">
-        <v>14.9</v>
-      </c>
-      <c r="I7" s="14">
-        <v>18.7</v>
-      </c>
-      <c r="J7" s="14">
-        <v>26.3</v>
-      </c>
-      <c r="K7" s="14">
-        <v>25.5</v>
-      </c>
-      <c r="L7" s="14">
-        <v>23.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D8" s="15">
-        <v>20.568799401966807</v>
-      </c>
-      <c r="E8" s="15">
-        <v>16</v>
-      </c>
-      <c r="F8" s="15">
-        <v>14.8</v>
-      </c>
-      <c r="G8" s="15">
-        <v>13.6</v>
-      </c>
-      <c r="H8" s="35">
-        <v>10.5</v>
-      </c>
-      <c r="I8" s="35">
-        <v>14.9</v>
-      </c>
-      <c r="J8" s="15">
-        <v>22</v>
-      </c>
-      <c r="K8" s="35">
-        <v>22.3</v>
-      </c>
-      <c r="L8" s="35">
-        <v>19.899999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="43"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="22">
-        <v>23.727491891830027</v>
-      </c>
-      <c r="E10" s="22">
-        <v>18.981761935247256</v>
-      </c>
-      <c r="F10" s="22">
-        <v>14.748616757210716</v>
-      </c>
-      <c r="G10" s="22">
-        <v>12.56931186247461</v>
-      </c>
-      <c r="H10" s="31">
-        <v>6.6</v>
-      </c>
-      <c r="I10" s="31">
-        <v>11.4</v>
-      </c>
-      <c r="J10" s="31">
-        <v>18</v>
-      </c>
-      <c r="K10" s="31">
-        <v>18</v>
-      </c>
-      <c r="L10" s="31">
-        <v>17.100000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="22">
-        <v>19.900404104368668</v>
-      </c>
-      <c r="E11" s="22">
-        <v>18.030501185267081</v>
-      </c>
-      <c r="F11" s="22">
-        <v>13.948052664523717</v>
-      </c>
-      <c r="G11" s="22">
-        <v>10.713886021727234</v>
-      </c>
-      <c r="H11" s="31">
-        <v>8.1</v>
-      </c>
-      <c r="I11" s="31">
-        <v>8.9</v>
-      </c>
-      <c r="J11" s="31">
-        <v>17.2</v>
-      </c>
-      <c r="K11" s="31">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="L11" s="31">
-        <v>14.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="22">
-        <v>20.936837214778837</v>
-      </c>
-      <c r="E12" s="22">
-        <v>17.480641986834843</v>
-      </c>
-      <c r="F12" s="22">
-        <v>18.451453227304977</v>
-      </c>
-      <c r="G12" s="22">
-        <v>15.811220408739953</v>
-      </c>
-      <c r="H12" s="22">
-        <v>11.1</v>
-      </c>
-      <c r="I12" s="22">
-        <v>15.3</v>
-      </c>
-      <c r="J12" s="22">
-        <v>23.2</v>
-      </c>
-      <c r="K12" s="22">
-        <v>21.3</v>
-      </c>
-      <c r="L12" s="22">
-        <v>16.899999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="22">
-        <v>31.941973691113994</v>
-      </c>
-      <c r="E13" s="22">
-        <v>22.514499275320098</v>
-      </c>
-      <c r="F13" s="22">
-        <v>22.859645557225814</v>
-      </c>
-      <c r="G13" s="22">
-        <v>18.364476580609249</v>
-      </c>
-      <c r="H13" s="22">
-        <v>17.100000000000001</v>
-      </c>
-      <c r="I13" s="22">
-        <v>22.1</v>
-      </c>
-      <c r="J13" s="22">
-        <v>29.1</v>
-      </c>
-      <c r="K13" s="22">
-        <v>30.2</v>
-      </c>
-      <c r="L13" s="22">
-        <v>29.1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="22">
-        <v>33.358438093348205</v>
-      </c>
-      <c r="E14" s="22">
-        <v>27.556783086958745</v>
-      </c>
-      <c r="F14" s="22">
-        <v>26.449236982189937</v>
-      </c>
-      <c r="G14" s="22">
-        <v>23.421118218014087</v>
-      </c>
-      <c r="H14" s="22">
-        <v>25</v>
-      </c>
-      <c r="I14" s="22">
-        <v>27.5</v>
-      </c>
-      <c r="J14" s="22">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="K14" s="22">
-        <v>31.7</v>
-      </c>
-      <c r="L14" s="22">
-        <v>28.3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="22">
-        <v>27.540969086733867</v>
-      </c>
-      <c r="E15" s="22">
-        <v>20.070138927127417</v>
-      </c>
-      <c r="F15" s="22">
-        <v>21.848722918967393</v>
-      </c>
-      <c r="G15" s="22">
-        <v>18.51925367661957</v>
-      </c>
-      <c r="H15" s="22">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="I15" s="22">
-        <v>25.2</v>
-      </c>
-      <c r="J15" s="22">
-        <v>33.4</v>
-      </c>
-      <c r="K15" s="22">
-        <v>34.1</v>
-      </c>
-      <c r="L15" s="22">
-        <v>33.4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="22">
-        <v>20.291456975420921</v>
-      </c>
-      <c r="E16" s="22">
-        <v>15.102516529601948</v>
-      </c>
-      <c r="F16" s="22">
-        <v>15.280590240825578</v>
-      </c>
-      <c r="G16" s="22">
-        <v>13.517279633635679</v>
-      </c>
-      <c r="H16" s="22">
-        <v>11.1</v>
-      </c>
-      <c r="I16" s="22">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="J16" s="22">
-        <v>26.4</v>
-      </c>
-      <c r="K16" s="22">
-        <v>25.8</v>
-      </c>
-      <c r="L16" s="22">
-        <v>22.1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="22">
-        <v>12.363589530005411</v>
-      </c>
-      <c r="E17" s="22">
-        <v>11.302523667429019</v>
-      </c>
-      <c r="F17" s="22">
-        <v>10.786084047642252</v>
-      </c>
-      <c r="G17" s="22">
-        <v>12.477862268683602</v>
-      </c>
-      <c r="H17" s="22">
-        <v>8.6</v>
-      </c>
-      <c r="I17" s="22">
-        <v>12.3</v>
-      </c>
-      <c r="J17" s="22">
-        <v>20.100000000000001</v>
-      </c>
-      <c r="K17" s="22">
-        <v>20</v>
-      </c>
-      <c r="L17" s="22">
-        <v>16.600000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="22">
-        <v>11.3934157044781</v>
-      </c>
-      <c r="E18" s="22">
-        <v>8.3983705266624522</v>
-      </c>
-      <c r="F18" s="22">
-        <v>10.34486128229991</v>
-      </c>
-      <c r="G18" s="22">
-        <v>9.4892565740388939</v>
-      </c>
-      <c r="H18" s="22">
-        <v>7.9</v>
-      </c>
-      <c r="I18" s="22">
-        <v>8.9</v>
-      </c>
-      <c r="J18" s="22">
-        <v>13</v>
-      </c>
-      <c r="K18" s="22">
-        <v>12.1</v>
-      </c>
-      <c r="L18" s="22">
-        <v>14.7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="22">
-        <v>9.4370766036096025</v>
-      </c>
-      <c r="E19" s="22">
-        <v>14.236349327004385</v>
-      </c>
-      <c r="F19" s="22">
-        <v>14.339166341825397</v>
-      </c>
-      <c r="G19" s="22">
-        <v>11.956666877329058</v>
-      </c>
-      <c r="H19" s="22">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="I19" s="22">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="J19" s="22">
-        <v>14.3</v>
-      </c>
-      <c r="K19" s="22">
-        <v>10.3</v>
-      </c>
-      <c r="L19" s="22">
-        <v>9.1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="22">
-        <v>5.3483560499368208</v>
-      </c>
-      <c r="E20" s="22">
-        <v>7.6176247728212596</v>
-      </c>
-      <c r="F20" s="22">
-        <v>6.1521676850850815</v>
-      </c>
-      <c r="G20" s="22">
-        <v>4.7759391183563746</v>
-      </c>
-      <c r="H20" s="22">
-        <v>4.2</v>
-      </c>
-      <c r="I20" s="22">
-        <v>9.4</v>
-      </c>
-      <c r="J20" s="22">
-        <v>17.100000000000001</v>
-      </c>
-      <c r="K20" s="22">
-        <v>15.1</v>
-      </c>
-      <c r="L20" s="22">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="22">
-        <v>4.3248118918794747</v>
-      </c>
-      <c r="E21" s="22">
-        <v>13.92994136929909</v>
-      </c>
-      <c r="F21" s="22">
-        <v>10.576621203348067</v>
-      </c>
-      <c r="G21" s="22">
-        <v>3.7174719620012309</v>
-      </c>
-      <c r="H21" s="22">
-        <v>7.3</v>
-      </c>
-      <c r="I21" s="22">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="J21" s="22">
-        <v>13.6</v>
-      </c>
-      <c r="K21" s="22">
-        <v>12.1</v>
-      </c>
-      <c r="L21" s="22">
-        <v>11.6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="B22" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="42"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="34"/>
-    </row>
-    <row r="23" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="D23" s="14">
-        <v>18.096777347528821</v>
-      </c>
-      <c r="E23" s="14">
-        <v>11.846666849488686</v>
-      </c>
-      <c r="F23" s="14">
-        <v>13.174611461584712</v>
-      </c>
-      <c r="G23" s="14">
-        <v>13</v>
-      </c>
-      <c r="H23" s="32">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="I23" s="32">
-        <v>12.4</v>
-      </c>
-      <c r="J23" s="14">
-        <v>24.8</v>
-      </c>
-      <c r="K23" s="32">
-        <v>25.9</v>
-      </c>
-      <c r="L23" s="32">
-        <v>22.6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" s="15">
-        <v>25.484816175693549</v>
-      </c>
-      <c r="E24" s="15">
-        <v>21.760369334408139</v>
-      </c>
-      <c r="F24" s="15">
-        <v>20.74075673507425</v>
-      </c>
-      <c r="G24" s="15">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="H24" s="32">
-        <v>15.2</v>
-      </c>
-      <c r="I24" s="32">
-        <v>20.100000000000001</v>
-      </c>
-      <c r="J24" s="15">
-        <v>24.6</v>
-      </c>
-      <c r="K24" s="32">
-        <v>23.2</v>
-      </c>
-      <c r="L24" s="32">
-        <v>21.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="B25" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="43"/>
-      <c r="K25" s="36"/>
-      <c r="L25" s="36"/>
-    </row>
-    <row r="26" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A26" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D26" s="22">
-        <v>29.143908007004935</v>
-      </c>
-      <c r="E26" s="22">
-        <v>24.458296607773754</v>
-      </c>
-      <c r="F26" s="22">
-        <v>22.569517630180179</v>
-      </c>
-      <c r="G26" s="22">
-        <v>21.917680212784951</v>
-      </c>
-      <c r="H26" s="32">
-        <v>14.2</v>
-      </c>
-      <c r="I26" s="32">
-        <v>21.1</v>
-      </c>
-      <c r="J26" s="32">
-        <v>24.3</v>
-      </c>
-      <c r="K26" s="32">
-        <v>25.9</v>
-      </c>
-      <c r="L26" s="32">
-        <v>24.3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="22">
-        <v>25.706732621123876</v>
-      </c>
-      <c r="E27" s="22">
-        <v>17.407081439088394</v>
-      </c>
-      <c r="F27" s="22">
-        <v>43.485033074010154</v>
-      </c>
-      <c r="G27" s="22">
-        <v>46.524661279291919</v>
-      </c>
-      <c r="H27" s="32">
-        <v>40.4</v>
-      </c>
-      <c r="I27" s="32">
-        <v>40.1</v>
-      </c>
-      <c r="J27" s="32">
-        <v>47.1</v>
-      </c>
-      <c r="K27" s="32">
-        <v>48.3</v>
-      </c>
-      <c r="L27" s="32">
-        <v>44.96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" s="22">
-        <v>20.686606210854819</v>
-      </c>
-      <c r="E28" s="22">
-        <v>16.804166833395346</v>
-      </c>
-      <c r="F28" s="22">
-        <v>19.252254610641589</v>
-      </c>
-      <c r="G28" s="22">
-        <v>12.973926140370661</v>
-      </c>
-      <c r="H28" s="32">
-        <v>14.3</v>
-      </c>
-      <c r="I28" s="32">
-        <v>13.5</v>
-      </c>
-      <c r="J28" s="32">
-        <v>23.6</v>
-      </c>
-      <c r="K28" s="32">
-        <v>24.3</v>
-      </c>
-      <c r="L28" s="32">
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A29" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="22">
-        <v>10.380818288468426</v>
-      </c>
-      <c r="E29" s="22">
-        <v>6.694579441234457</v>
-      </c>
-      <c r="F29" s="22">
-        <v>16.766197552453242</v>
-      </c>
-      <c r="G29" s="22">
-        <v>9.8700006382711329</v>
-      </c>
-      <c r="H29" s="32">
-        <v>10</v>
-      </c>
-      <c r="I29" s="32">
-        <v>18.7</v>
-      </c>
-      <c r="J29" s="32">
-        <v>28.8</v>
-      </c>
-      <c r="K29" s="32">
-        <v>28.1</v>
-      </c>
-      <c r="L29" s="32">
-        <v>17.399999999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="36" x14ac:dyDescent="0.25">
-      <c r="A30" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" s="22">
-        <v>8.7634580318953859</v>
-      </c>
-      <c r="E30" s="22">
-        <v>11.046114565895568</v>
-      </c>
-      <c r="F30" s="22">
-        <v>16.935337550642007</v>
-      </c>
-      <c r="G30" s="22">
-        <v>14.440148321432762</v>
-      </c>
-      <c r="H30" s="32">
-        <v>16.3</v>
-      </c>
-      <c r="I30" s="32">
-        <v>24.4</v>
-      </c>
-      <c r="J30" s="32">
-        <v>27.8</v>
-      </c>
-      <c r="K30" s="32">
-        <v>25.8</v>
-      </c>
-      <c r="L30" s="32">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="D31" s="22">
-        <v>30.479758516587125</v>
-      </c>
-      <c r="E31" s="22">
-        <v>21.910700739938726</v>
-      </c>
-      <c r="F31" s="22">
-        <v>25.189652676651377</v>
-      </c>
-      <c r="G31" s="22">
-        <v>18.342747525957986</v>
-      </c>
-      <c r="H31" s="32">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="I31" s="32">
-        <v>21.6</v>
-      </c>
-      <c r="J31" s="32">
-        <v>29.9</v>
-      </c>
-      <c r="K31" s="32">
-        <v>27.1</v>
-      </c>
-      <c r="L31" s="32">
-        <v>25.3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A32" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="B32" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="C32" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="D32" s="22">
-        <v>17.048203277049947</v>
-      </c>
-      <c r="E32" s="22">
-        <v>13.904378994106649</v>
-      </c>
-      <c r="F32" s="22">
-        <v>12.6648830342567</v>
-      </c>
-      <c r="G32" s="22">
-        <v>12.403590756556879</v>
-      </c>
-      <c r="H32" s="32">
-        <v>11.6</v>
-      </c>
-      <c r="I32" s="32">
-        <v>10.1</v>
-      </c>
-      <c r="J32" s="32">
-        <v>20.7</v>
-      </c>
-      <c r="K32" s="32">
-        <v>20.7</v>
-      </c>
-      <c r="L32" s="32">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="B33" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="D33" s="22">
-        <v>22.274049816094269</v>
-      </c>
-      <c r="E33" s="22">
-        <v>20.940255499025756</v>
-      </c>
-      <c r="F33" s="22">
-        <v>17.991689994650695</v>
-      </c>
-      <c r="G33" s="22">
-        <v>14.19051856054139</v>
-      </c>
-      <c r="H33" s="32">
-        <v>15.2</v>
-      </c>
-      <c r="I33" s="32">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="J33" s="32">
-        <v>26.2</v>
-      </c>
-      <c r="K33" s="32">
-        <v>24.3</v>
-      </c>
-      <c r="L33" s="32">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A34" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="B34" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="D34" s="22">
-        <v>18.210339702711089</v>
-      </c>
-      <c r="E34" s="22">
-        <v>13.950839004406477</v>
-      </c>
-      <c r="F34" s="22">
-        <v>10.454912304521647</v>
-      </c>
-      <c r="G34" s="22">
-        <v>10.100326551559347</v>
-      </c>
-      <c r="H34" s="32">
-        <v>8.9</v>
-      </c>
-      <c r="I34" s="32">
-        <v>11.6</v>
-      </c>
-      <c r="J34" s="32">
-        <v>19.100000000000001</v>
-      </c>
-      <c r="K34" s="32">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="L34" s="32">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="B35" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D35" s="22">
-        <v>23.378289047105444</v>
-      </c>
-      <c r="E35" s="22">
-        <v>12.552140899407622</v>
-      </c>
-      <c r="F35" s="22">
-        <v>7.2176300468835244</v>
-      </c>
-      <c r="G35" s="22">
-        <v>7.398290201001557</v>
-      </c>
-      <c r="H35" s="32">
-        <v>2.1</v>
-      </c>
-      <c r="I35" s="32">
-        <v>5.3</v>
-      </c>
-      <c r="J35" s="32">
-        <v>10.7</v>
-      </c>
-      <c r="K35" s="32">
-        <v>7.5</v>
-      </c>
-      <c r="L35" s="32">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="B36" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="D36" s="22">
-        <v>10.489031113365179</v>
-      </c>
-      <c r="E36" s="22">
-        <v>6.9730957623240366</v>
-      </c>
-      <c r="F36" s="22">
-        <v>11.910368149341213</v>
-      </c>
-      <c r="G36" s="22">
-        <v>10.729114750103726</v>
-      </c>
-      <c r="H36" s="32">
-        <v>15.6</v>
-      </c>
-      <c r="I36" s="32">
-        <v>20.5</v>
-      </c>
-      <c r="J36" s="32">
-        <v>28.9</v>
-      </c>
-      <c r="K36" s="32">
-        <v>11.4</v>
-      </c>
-      <c r="L36" s="32">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="B37" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D37" s="22">
-        <v>3.9345552103031651</v>
-      </c>
-      <c r="E37" s="22">
-        <v>1.5610395489662543</v>
-      </c>
-      <c r="F37" s="22">
-        <v>1.8769969620631242</v>
-      </c>
-      <c r="G37" s="24"/>
-      <c r="H37" s="34"/>
-      <c r="I37" s="40">
-        <v>9</v>
-      </c>
-      <c r="J37" s="32">
-        <v>22.7</v>
-      </c>
-      <c r="K37" s="40">
-        <v>36.5</v>
-      </c>
-      <c r="L37" s="40">
-        <v>39.200000000000003</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A38" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="B38" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="C38" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D38" s="17">
-        <v>18.961062865334473</v>
-      </c>
-      <c r="E38" s="17">
-        <v>6.4150369668849034</v>
-      </c>
-      <c r="F38" s="17">
-        <v>10.73328466572039</v>
-      </c>
-      <c r="G38" s="17">
-        <v>6.1871817427579057</v>
-      </c>
-      <c r="H38" s="32">
-        <v>12.6</v>
-      </c>
-      <c r="I38" s="32">
-        <v>21</v>
-      </c>
-      <c r="J38" s="32">
-        <v>17.899999999999999</v>
-      </c>
-      <c r="K38" s="32">
-        <v>17.8</v>
-      </c>
-      <c r="L38" s="32">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A39" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="B39" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="C39" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D39" s="17">
-        <v>13.647895195863507</v>
-      </c>
-      <c r="E39" s="17">
-        <v>9.7394396593161634</v>
-      </c>
-      <c r="F39" s="17">
-        <v>17.445705080152951</v>
-      </c>
-      <c r="G39" s="17">
-        <v>10.903917301963624</v>
-      </c>
-      <c r="H39" s="32">
-        <v>10.8</v>
-      </c>
-      <c r="I39" s="32">
-        <v>12</v>
-      </c>
-      <c r="J39" s="32">
-        <v>24.9</v>
-      </c>
-      <c r="K39" s="32">
-        <v>20.3</v>
-      </c>
-      <c r="L39" s="32">
-        <v>41.3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A40" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="B40" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C40" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="D40" s="17">
-        <v>16.876778837009706</v>
-      </c>
-      <c r="E40" s="17">
-        <v>9.9482201054391233</v>
-      </c>
-      <c r="F40" s="17">
-        <v>10.126908927702534</v>
-      </c>
-      <c r="G40" s="17">
-        <v>6.6467604972894136</v>
-      </c>
-      <c r="H40" s="32">
-        <v>6.7</v>
-      </c>
-      <c r="I40" s="32">
-        <v>13.1</v>
-      </c>
-      <c r="J40" s="32">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="K40" s="32">
-        <v>20.5</v>
-      </c>
-      <c r="L40" s="32">
-        <v>17.399999999999999</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="B41" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C41" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D41" s="17">
-        <v>20.413163685010215</v>
-      </c>
-      <c r="E41" s="17">
-        <v>16.145522408727153</v>
-      </c>
-      <c r="F41" s="17">
-        <v>18.579279969160616</v>
-      </c>
-      <c r="G41" s="17">
-        <v>18.915134715736656</v>
-      </c>
-      <c r="H41" s="32">
-        <v>13.2</v>
-      </c>
-      <c r="I41" s="32">
-        <v>22</v>
-      </c>
-      <c r="J41" s="32">
-        <v>30.7</v>
-      </c>
-      <c r="K41" s="32">
-        <v>32.200000000000003</v>
-      </c>
-      <c r="L41" s="32">
-        <v>25.6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A42" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="B42" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D42" s="22">
-        <v>13.310295070774758</v>
-      </c>
-      <c r="E42" s="22">
-        <v>11.612557015790795</v>
-      </c>
-      <c r="F42" s="22">
-        <v>15.172329167457105</v>
-      </c>
-      <c r="G42" s="22">
-        <v>12.02603404393124</v>
-      </c>
-      <c r="H42" s="32">
-        <v>10.9</v>
-      </c>
-      <c r="I42" s="32">
-        <v>22.9</v>
-      </c>
-      <c r="J42" s="32">
-        <v>25.1</v>
-      </c>
-      <c r="K42" s="32">
-        <v>23.2</v>
-      </c>
-      <c r="L42" s="32">
-        <v>18.899999999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="B43" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="C43" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="D43" s="22">
-        <v>24.880927816476003</v>
-      </c>
-      <c r="E43" s="22">
-        <v>22.865183692499258</v>
-      </c>
-      <c r="F43" s="22">
-        <v>13.457394959480895</v>
-      </c>
-      <c r="G43" s="22">
-        <v>9.9681806468962222</v>
-      </c>
-      <c r="H43" s="32">
-        <v>13.3</v>
-      </c>
-      <c r="I43" s="32">
-        <v>12.6</v>
-      </c>
-      <c r="J43" s="32">
-        <v>16.3</v>
-      </c>
-      <c r="K43" s="32">
-        <v>23.8</v>
-      </c>
-      <c r="L43" s="32">
-        <v>15.3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="B44" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="C44" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="D44" s="22">
-        <v>14.316550849178517</v>
-      </c>
-      <c r="E44" s="22">
-        <v>10.525974149433518</v>
-      </c>
-      <c r="F44" s="22">
-        <v>9.6502437264322651</v>
-      </c>
-      <c r="G44" s="22">
-        <v>9.1216159509677954</v>
-      </c>
-      <c r="H44" s="32">
-        <v>6.8</v>
-      </c>
-      <c r="I44" s="32">
-        <v>12.5</v>
-      </c>
-      <c r="J44" s="32">
-        <v>24.3</v>
-      </c>
-      <c r="K44" s="32">
-        <v>21</v>
-      </c>
-      <c r="L44" s="32">
-        <v>18.100000000000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="B45" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="C45" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="D45" s="22">
-        <v>23.958709378309926</v>
-      </c>
-      <c r="E45" s="22">
-        <v>46.915523465793008</v>
-      </c>
-      <c r="F45" s="22">
-        <v>31.481607442776532</v>
-      </c>
-      <c r="G45" s="22">
-        <v>23.380874333038371</v>
-      </c>
-      <c r="H45" s="32">
-        <v>18.3</v>
-      </c>
-      <c r="I45" s="32">
-        <v>36</v>
-      </c>
-      <c r="J45" s="32">
-        <v>20.6</v>
-      </c>
-      <c r="K45" s="32">
-        <v>18</v>
-      </c>
-      <c r="L45" s="32">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="B46" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="C46" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="D46" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="E46" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="F46" s="28">
-        <v>15.59978614323523</v>
-      </c>
-      <c r="G46" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="H46" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="I46" s="28">
-        <v>10.7</v>
-      </c>
-      <c r="J46" s="44" t="s">
-        <v>64</v>
-      </c>
-      <c r="K46" s="28">
-        <v>3.2</v>
-      </c>
-      <c r="L46" s="28">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="19"/>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="16"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
